--- a/R_Codes/DataSummary/Archaea/Sample_Type/Archaea_Summary_Class_by_Sample_Type.xlsx
+++ b/R_Codes/DataSummary/Archaea/Sample_Type/Archaea_Summary_Class_by_Sample_Type.xlsx
@@ -459,10 +459,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>18.5202533685736</v>
+        <v>18.5201013097571</v>
       </c>
       <c r="D2" t="n">
-        <v>0.505976770488784</v>
+        <v>0.505976909932865</v>
       </c>
     </row>
     <row r="3">
@@ -473,10 +473,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>16.7496098664917</v>
+        <v>16.7453301923525</v>
       </c>
       <c r="D3" t="n">
-        <v>2.96408088351006</v>
+        <v>2.9630776468081</v>
       </c>
     </row>
     <row r="4">
@@ -487,10 +487,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>12.6800338133721</v>
+        <v>12.6804160381113</v>
       </c>
       <c r="D4" t="n">
-        <v>0.423578860668056</v>
+        <v>0.423591198619781</v>
       </c>
     </row>
     <row r="5">
@@ -501,10 +501,10 @@
         <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>12.3021921641972</v>
+        <v>12.3026594588541</v>
       </c>
       <c r="D5" t="n">
-        <v>0.680026350575475</v>
+        <v>0.680014840542453</v>
       </c>
     </row>
     <row r="6">
@@ -515,10 +515,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>11.7452341318612</v>
+        <v>11.7458348323098</v>
       </c>
       <c r="D6" t="n">
-        <v>1.37682566368649</v>
+        <v>1.37689345146925</v>
       </c>
     </row>
     <row r="7">
@@ -529,10 +529,10 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>6.95538214449839</v>
+        <v>6.95653878385309</v>
       </c>
       <c r="D7" t="n">
-        <v>0.051641360466749</v>
+        <v>0.0516579124591188</v>
       </c>
     </row>
     <row r="8">
@@ -543,10 +543,10 @@
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>6.25422579699541</v>
+        <v>6.25509725438493</v>
       </c>
       <c r="D8" t="n">
-        <v>3.99436845805551</v>
+        <v>3.99503421260845</v>
       </c>
     </row>
     <row r="9">
@@ -557,10 +557,10 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>6.11588517287203</v>
+        <v>6.1164324484389</v>
       </c>
       <c r="D9" t="n">
-        <v>0.616074763446808</v>
+        <v>0.616147299562352</v>
       </c>
     </row>
     <row r="10">
@@ -571,10 +571,10 @@
         <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>2.19994636630155</v>
+        <v>2.1998961256231</v>
       </c>
       <c r="D10" t="n">
-        <v>0.107160564694792</v>
+        <v>0.107160590329108</v>
       </c>
     </row>
     <row r="11">
@@ -585,10 +585,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>1.46754394593324</v>
+        <v>1.46756821441988</v>
       </c>
       <c r="D11" t="n">
-        <v>0.221908676469357</v>
+        <v>0.221914596352504</v>
       </c>
     </row>
     <row r="12">
@@ -599,10 +599,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>1.46564892526542</v>
+        <v>1.46612663342029</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0466877372539877</v>
+        <v>0.0467043258433747</v>
       </c>
     </row>
     <row r="13">
@@ -613,10 +613,10 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>0.939262261327925</v>
+        <v>0.939235706664847</v>
       </c>
       <c r="D13" t="n">
-        <v>0.076588972054449</v>
+        <v>0.0765853287362225</v>
       </c>
     </row>
     <row r="14">
@@ -627,10 +627,10 @@
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>0.922485621046044</v>
+        <v>0.922428448465171</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0956601710709274</v>
+        <v>0.0956434026846114</v>
       </c>
     </row>
     <row r="15">
@@ -641,10 +641,10 @@
         <v>18</v>
       </c>
       <c r="C15" t="n">
-        <v>0.702726037156627</v>
+        <v>0.702697770525482</v>
       </c>
       <c r="D15" t="n">
-        <v>0.187953862659956</v>
+        <v>0.187943863450388</v>
       </c>
     </row>
     <row r="16">
@@ -655,10 +655,10 @@
         <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>0.373053088548069</v>
+        <v>0.373104243580127</v>
       </c>
       <c r="D16" t="n">
-        <v>0.115024472265287</v>
+        <v>0.115042827780335</v>
       </c>
     </row>
     <row r="17">
@@ -669,10 +669,10 @@
         <v>20</v>
       </c>
       <c r="C17" t="n">
-        <v>0.140690285136584</v>
+        <v>0.140685141227975</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0128404769835274</v>
+        <v>0.0128378141578971</v>
       </c>
     </row>
     <row r="18">
@@ -683,10 +683,10 @@
         <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>0.139326797297523</v>
+        <v>0.139357882061933</v>
       </c>
       <c r="D18" t="n">
-        <v>0.00657364646947169</v>
+        <v>0.00657574523047377</v>
       </c>
     </row>
     <row r="19">
@@ -697,10 +697,10 @@
         <v>22</v>
       </c>
       <c r="C19" t="n">
-        <v>0.114960544008385</v>
+        <v>0.114961862604409</v>
       </c>
       <c r="D19" t="n">
-        <v>0.032622598907635</v>
+        <v>0.0326241618178361</v>
       </c>
     </row>
     <row r="20">
@@ -711,10 +711,10 @@
         <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0803675904299304</v>
+        <v>0.08037041417289</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0353534956882546</v>
+        <v>0.0353555078309078</v>
       </c>
     </row>
     <row r="21">
@@ -725,10 +725,10 @@
         <v>24</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0757661709457359</v>
+        <v>0.0757499067335201</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0524181217803904</v>
+        <v>0.0524055170092779</v>
       </c>
     </row>
     <row r="22">
@@ -739,7 +739,7 @@
         <v>25</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0301708776892948</v>
+        <v>0.0301647251607637</v>
       </c>
       <c r="D22"/>
     </row>
@@ -751,7 +751,7 @@
         <v>26</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0230510669255519</v>
+        <v>0.0230564187299055</v>
       </c>
       <c r="D23"/>
     </row>
@@ -763,7 +763,7 @@
         <v>27</v>
       </c>
       <c r="C24" t="n">
-        <v>0.00218396312648901</v>
+        <v>0.00218618854804676</v>
       </c>
       <c r="D24"/>
     </row>
@@ -800,10 +800,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>54.1129255454368</v>
+        <v>54.2903931518093</v>
       </c>
       <c r="D2" t="n">
-        <v>10.2494138186117</v>
+        <v>10.2900236788944</v>
       </c>
     </row>
     <row r="3">
@@ -814,10 +814,10 @@
         <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>24.0089554710508</v>
+        <v>23.9509554304592</v>
       </c>
       <c r="D3" t="n">
-        <v>0.238203648998989</v>
+        <v>0.237575554856321</v>
       </c>
     </row>
     <row r="4">
@@ -828,10 +828,10 @@
         <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>5.60580054516845</v>
+        <v>5.56924494107659</v>
       </c>
       <c r="D4" t="n">
-        <v>0.580672928149858</v>
+        <v>0.578594848887287</v>
       </c>
     </row>
     <row r="5">
@@ -842,10 +842,10 @@
         <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>3.7364525370258</v>
+        <v>3.72619530103943</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0604065991966392</v>
+        <v>0.0602198697114108</v>
       </c>
     </row>
     <row r="6">
@@ -856,10 +856,10 @@
         <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>3.25624144156281</v>
+        <v>3.20771518374125</v>
       </c>
       <c r="D6" t="n">
-        <v>0.396554871331314</v>
+        <v>0.387417481863529</v>
       </c>
     </row>
     <row r="7">
@@ -870,10 +870,10 @@
         <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>2.38068014178256</v>
+        <v>2.37341644833467</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0576789885094573</v>
+        <v>0.0575256732831891</v>
       </c>
     </row>
     <row r="8">
@@ -884,10 +884,10 @@
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>2.3714300919777</v>
+        <v>2.36654661741218</v>
       </c>
       <c r="D8" t="n">
-        <v>0.619525480262922</v>
+        <v>0.618148293180579</v>
       </c>
     </row>
     <row r="9">
@@ -898,10 +898,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>1.44257685920316</v>
+        <v>1.43906660564869</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0493847440262116</v>
+        <v>0.0492352887412829</v>
       </c>
     </row>
     <row r="10">
@@ -912,10 +912,10 @@
         <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>1.33806010957939</v>
+        <v>1.33493156727963</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0554804762621068</v>
+        <v>0.0553380949128403</v>
       </c>
     </row>
     <row r="11">
@@ -926,10 +926,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>0.509258253215987</v>
+        <v>0.508486644638778</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0463705023945219</v>
+        <v>0.0462714911307914</v>
       </c>
     </row>
     <row r="12">
@@ -940,10 +940,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>0.418237393102326</v>
+        <v>0.417060694344558</v>
       </c>
       <c r="D12" t="n">
-        <v>0.164955414331459</v>
+        <v>0.164491248245208</v>
       </c>
     </row>
     <row r="13">
@@ -954,10 +954,10 @@
         <v>26</v>
       </c>
       <c r="C13" t="n">
-        <v>0.351612305902911</v>
+        <v>0.351483052903812</v>
       </c>
       <c r="D13" t="n">
-        <v>0.155646830278538</v>
+        <v>0.155638374117642</v>
       </c>
     </row>
     <row r="14">
@@ -968,10 +968,10 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>0.202909538947346</v>
+        <v>0.200269945495604</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0110467151095926</v>
+        <v>0.0107855099896259</v>
       </c>
     </row>
     <row r="15">
@@ -982,10 +982,10 @@
         <v>23</v>
       </c>
       <c r="C15" t="n">
-        <v>0.130528137955803</v>
+        <v>0.130137596240074</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0802984118142438</v>
+        <v>0.0800461302400138</v>
       </c>
     </row>
     <row r="16">
@@ -996,10 +996,10 @@
         <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>0.031028231306782</v>
+        <v>0.0309894801565336</v>
       </c>
       <c r="D16" t="n">
-        <v>0.00584097358048779</v>
+        <v>0.00583147820982544</v>
       </c>
     </row>
     <row r="17">
@@ -1010,7 +1010,7 @@
         <v>22</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0296149408341879</v>
+        <v>0.0295685255181075</v>
       </c>
       <c r="D17"/>
     </row>
@@ -1022,10 +1022,10 @@
         <v>14</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0287377020477431</v>
+        <v>0.0286789171097611</v>
       </c>
       <c r="D18" t="n">
-        <v>0.00414494693494354</v>
+        <v>0.0041369753964699</v>
       </c>
     </row>
     <row r="19">
@@ -1036,10 +1036,10 @@
         <v>17</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0214075508501126</v>
+        <v>0.0213649759054163</v>
       </c>
       <c r="D19" t="n">
-        <v>0.00582731581784547</v>
+        <v>0.00581331564038483</v>
       </c>
     </row>
     <row r="20">
@@ -1050,10 +1050,10 @@
         <v>18</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0112981671212124</v>
+        <v>0.0112786167875188</v>
       </c>
       <c r="D20" t="n">
-        <v>0.00220970538097561</v>
+        <v>0.00220594438459289</v>
       </c>
     </row>
     <row r="21">
@@ -1064,7 +1064,7 @@
         <v>25</v>
       </c>
       <c r="C21" t="n">
-        <v>0.00336541783215633</v>
+        <v>0.00335957532414269</v>
       </c>
       <c r="D21"/>
     </row>
@@ -1076,7 +1076,7 @@
         <v>29</v>
       </c>
       <c r="C22" t="n">
-        <v>0.00333010546463304</v>
+        <v>0.00331873303929328</v>
       </c>
       <c r="D22"/>
     </row>
@@ -1088,7 +1088,7 @@
         <v>20</v>
       </c>
       <c r="C23" t="n">
-        <v>0.00251404162474268</v>
+        <v>0.0025108092006458</v>
       </c>
       <c r="D23"/>
     </row>
@@ -1100,7 +1100,7 @@
         <v>24</v>
       </c>
       <c r="C24" t="n">
-        <v>0.00161919639026515</v>
+        <v>0.0016136667785894</v>
       </c>
       <c r="D24"/>
     </row>
@@ -1112,7 +1112,7 @@
         <v>30</v>
       </c>
       <c r="C25" t="n">
-        <v>0.000961590582669442</v>
+        <v>0.000959892825720676</v>
       </c>
       <c r="D25"/>
     </row>
@@ -1124,7 +1124,7 @@
         <v>31</v>
       </c>
       <c r="C26" t="n">
-        <v>0.000454684033659048</v>
+        <v>0.000453626930754705</v>
       </c>
       <c r="D26"/>
     </row>
